--- a/Tests Data/Kyocera KC85TS/Single diode model/G = 400 W.m^-2 and T = 25ºC/R load/Single-diode emulator - R - Kyocera KC85TS (ref = STC, G = 400 and T = 25).xlsx
+++ b/Tests Data/Kyocera KC85TS/Single diode model/G = 400 W.m^-2 and T = 25ºC/R load/Single-diode emulator - R - Kyocera KC85TS (ref = STC, G = 400 and T = 25).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\Test Data - new\Kyocera KC85TS\Single diode model\G = 400 W.m^-2 and T = 25ºC\R load\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\PV-emulator\Tests Data\Kyocera KC85TS\Single diode model\G = 400 W.m^-2 and T = 25ºC\R load\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9938526-9C73-4FEC-B281-95BD8495FD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7ABE26-939A-4A49-8781-8080EDBAA06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
+    <workbookView xWindow="34785" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -537,57 +537,57 @@
         <v>60</v>
       </c>
       <c r="B2">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="C2">
         <f>A2*B2</f>
-        <v>15.600000000000001</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>3.92</v>
+        <v>4.12</v>
       </c>
       <c r="E2">
-        <v>2.0299999999999998</v>
+        <v>1.93</v>
       </c>
       <c r="F2">
         <f>D2*E2</f>
-        <v>7.9575999999999993</v>
+        <v>7.9516</v>
       </c>
       <c r="G2">
         <f>D2/E2</f>
-        <v>1.9310344827586208</v>
+        <v>2.1347150259067358</v>
       </c>
       <c r="H2">
-        <v>21.917355000000001</v>
+        <v>22.491886000000001</v>
       </c>
       <c r="I2">
-        <v>12.392923</v>
+        <v>11.192251000000001</v>
       </c>
       <c r="J2">
-        <v>3.7716889999999998</v>
+        <v>4.2908369999999998</v>
       </c>
       <c r="K2">
-        <v>2.13266</v>
+        <v>2.135176</v>
       </c>
       <c r="L2">
         <f>J2/K2</f>
-        <v>1.7685374133710952</v>
+        <v>2.0095940568833668</v>
       </c>
       <c r="M2">
         <f>ABS(J2-D2)/D2*100</f>
-        <v>3.7834438775510222</v>
+        <v>4.1465291262135846</v>
       </c>
       <c r="N2">
         <f>ABS(K2-E2)/E2*100</f>
-        <v>5.0571428571428667</v>
+        <v>10.630880829015545</v>
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O19" si="0">(ABS(L2-G2)/G2)*100</f>
-        <v>8.4150268075682906</v>
+        <v>5.8612492770655864</v>
       </c>
       <c r="P2">
         <f t="shared" ref="P2:P19" si="1">(F2/C2)*100</f>
-        <v>51.010256410256403</v>
+        <v>53.010666666666658</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -595,57 +595,57 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="C3">
         <f>A3*B3</f>
-        <v>30.6</v>
+        <v>27</v>
       </c>
       <c r="D3">
-        <v>11.57</v>
+        <v>9.94</v>
       </c>
       <c r="E3">
-        <v>2.06</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F3">
         <f>D3*E3</f>
-        <v>23.834200000000003</v>
+        <v>20.376999999999999</v>
       </c>
       <c r="G3">
         <f>D3/E3</f>
-        <v>5.616504854368932</v>
+        <v>4.8487804878048779</v>
       </c>
       <c r="H3">
-        <v>21.916889000000001</v>
+        <v>22.785145</v>
       </c>
       <c r="I3">
-        <v>3.961433</v>
+        <v>4.7978719999999999</v>
       </c>
       <c r="J3">
-        <v>11.757546</v>
+        <v>10.134062</v>
       </c>
       <c r="K3">
-        <v>2.1251530000000001</v>
+        <v>2.133931</v>
       </c>
       <c r="L3">
         <f>J3/K3</f>
-        <v>5.5325644788869317</v>
+        <v>4.7490110973597552</v>
       </c>
       <c r="M3">
         <f t="shared" ref="M3:M19" si="2">ABS(J3-D3)/D3*100</f>
-        <v>1.6209680207432957</v>
+        <v>1.9523340040241512</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N19" si="3">ABS(K3-E3)/E3*100</f>
-        <v>3.1627669902912632</v>
+        <v>4.0941951219512296</v>
       </c>
       <c r="O3">
         <f t="shared" si="0"/>
-        <v>1.4945304536985358</v>
+        <v>2.0576182134054473</v>
       </c>
       <c r="P3">
         <f t="shared" si="1"/>
-        <v>77.889542483660136</v>
+        <v>75.470370370370361</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -653,57 +653,57 @@
         <v>60</v>
       </c>
       <c r="B4">
-        <v>0.56000000000000005</v>
+        <v>0.54</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C16" si="4">A2*B4</f>
-        <v>33.6</v>
+        <v>32.400000000000006</v>
       </c>
       <c r="D4">
-        <v>13.3</v>
+        <v>12.48</v>
       </c>
       <c r="E4">
-        <v>2.0499999999999998</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="F4">
         <f>D4*E4</f>
-        <v>27.265000000000001</v>
+        <v>25.833600000000001</v>
       </c>
       <c r="G4">
         <f>D4/E4</f>
-        <v>6.4878048780487818</v>
+        <v>6.0289855072463778</v>
       </c>
       <c r="H4">
-        <v>21.917103000000001</v>
+        <v>22.494769999999999</v>
       </c>
       <c r="I4">
-        <v>3.4539110000000002</v>
+        <v>3.785123</v>
       </c>
       <c r="J4">
-        <v>13.46219</v>
+        <v>12.669167</v>
       </c>
       <c r="K4">
-        <v>2.1215030000000001</v>
+        <v>2.1318000000000001</v>
       </c>
       <c r="L4">
         <f>J4/K4</f>
-        <v>6.3455908381934876</v>
+        <v>5.9429435219063693</v>
       </c>
       <c r="M4">
         <f t="shared" si="2"/>
-        <v>1.2194736842105183</v>
+        <v>1.5157612179487132</v>
       </c>
       <c r="N4">
         <f t="shared" si="3"/>
-        <v>3.4879512195122109</v>
+        <v>2.9855072463768262</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>2.1920209150628054</v>
+        <v>1.4271386991491795</v>
       </c>
       <c r="P4">
         <f t="shared" si="1"/>
-        <v>81.145833333333329</v>
+        <v>79.73333333333332</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -711,57 +711,57 @@
         <v>60</v>
       </c>
       <c r="B5">
-        <v>0.62</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="C5">
         <f t="shared" si="4"/>
-        <v>37.200000000000003</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="D5">
-        <v>14.91</v>
+        <v>13.67</v>
       </c>
       <c r="E5" s="3">
-        <v>2.0699999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="F5">
         <f>D5*E5</f>
-        <v>30.863699999999998</v>
+        <v>28.707000000000001</v>
       </c>
       <c r="G5">
         <f>D5/E5</f>
-        <v>7.2028985507246386</v>
+        <v>6.5095238095238095</v>
       </c>
       <c r="H5">
-        <v>21.635138000000001</v>
+        <v>22.494724000000001</v>
       </c>
       <c r="I5">
-        <v>3.0400499999999999</v>
+        <v>3.4639980000000001</v>
       </c>
       <c r="J5">
-        <v>15.029916</v>
+        <v>13.826796999999999</v>
       </c>
       <c r="K5">
-        <v>2.11192</v>
+        <v>2.12921</v>
       </c>
       <c r="L5">
         <f t="shared" ref="L5:L15" si="5">J5/K5</f>
-        <v>7.1167070722375847</v>
+        <v>6.4938625123872225</v>
       </c>
       <c r="M5">
         <f t="shared" si="2"/>
-        <v>0.80426559356136762</v>
+        <v>1.1470153621067973</v>
       </c>
       <c r="N5">
         <f t="shared" si="3"/>
-        <v>2.0251207729468685</v>
+        <v>1.3909523809523789</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>1.1966221359369653</v>
+        <v>0.2405905192891937</v>
       </c>
       <c r="P5">
         <f t="shared" si="1"/>
-        <v>82.966935483870955</v>
+        <v>82.49137931034484</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -769,57 +769,57 @@
         <v>60</v>
       </c>
       <c r="B6">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="C6">
         <f t="shared" si="4"/>
-        <v>38.4</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="D6">
-        <v>15.59</v>
+        <v>14.87</v>
       </c>
       <c r="E6" s="3">
-        <v>2.0299999999999998</v>
+        <v>2.06</v>
       </c>
       <c r="F6">
         <f>D6*E6</f>
-        <v>31.647699999999997</v>
+        <v>30.632199999999997</v>
       </c>
       <c r="G6">
         <f>D6/E6</f>
-        <v>7.6798029556650249</v>
+        <v>7.2184466019417473</v>
       </c>
       <c r="H6">
-        <v>21.635173999999999</v>
+        <v>22.785276</v>
       </c>
       <c r="I6">
-        <v>2.8890829999999998</v>
+        <v>3.2200890000000002</v>
       </c>
       <c r="J6">
-        <v>15.72958</v>
+        <v>15.001448999999999</v>
       </c>
       <c r="K6">
-        <v>2.1004710000000002</v>
+        <v>2.120053</v>
       </c>
       <c r="L6">
         <f t="shared" ref="L6" si="6">J6/K6</f>
-        <v>7.4885966052375865</v>
+        <v>7.0759782892220144</v>
       </c>
       <c r="M6">
         <f t="shared" si="2"/>
-        <v>0.89531751122514747</v>
+        <v>0.88398789509078635</v>
       </c>
       <c r="N6">
         <f t="shared" si="3"/>
-        <v>3.4714778325123352</v>
+        <v>2.9151941747572772</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>2.4897298997286716</v>
+        <v>1.9736699677380607</v>
       </c>
       <c r="P6">
         <f t="shared" si="1"/>
-        <v>82.415885416666654</v>
+        <v>81.037566137566145</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -834,50 +834,50 @@
         <v>38.4</v>
       </c>
       <c r="D7">
-        <v>16.190000000000001</v>
+        <v>15.52</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="F7">
         <f t="shared" ref="F7" si="7">D7*E7</f>
-        <v>32.380000000000003</v>
+        <v>31.660799999999998</v>
       </c>
       <c r="G7">
         <f t="shared" ref="G7" si="8">D7/E7</f>
-        <v>8.0950000000000006</v>
+        <v>7.6078431372549016</v>
       </c>
       <c r="H7">
-        <v>21.635190999999999</v>
+        <v>22.492457999999999</v>
       </c>
       <c r="I7">
-        <v>2.7620429999999998</v>
+        <v>3.0394369999999999</v>
       </c>
       <c r="J7">
-        <v>16.312875999999999</v>
+        <v>15.612347</v>
       </c>
       <c r="K7">
-        <v>2.082573</v>
+        <v>2.109718</v>
       </c>
       <c r="L7">
         <f t="shared" si="5"/>
-        <v>7.8330392259959192</v>
+        <v>7.4002056198980144</v>
       </c>
       <c r="M7">
         <f t="shared" si="2"/>
-        <v>0.75896232242123518</v>
+        <v>0.59501932989690842</v>
       </c>
       <c r="N7">
         <f t="shared" si="3"/>
-        <v>4.1286500000000004</v>
+        <v>3.4175490196078409</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>3.2360812106742611</v>
+        <v>2.7292560271137236</v>
       </c>
       <c r="P7">
         <f t="shared" si="1"/>
-        <v>84.322916666666686</v>
+        <v>82.45</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -885,57 +885,57 @@
         <v>60</v>
       </c>
       <c r="B8">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="C8">
         <f t="shared" si="4"/>
-        <v>39.6</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>16.68</v>
+        <v>16.05</v>
       </c>
       <c r="E8">
-        <v>1.97</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F8">
         <f>D8*E8</f>
-        <v>32.8596</v>
+        <v>32.581499999999998</v>
       </c>
       <c r="G8">
         <f t="shared" ref="G8:G12" si="9">D8/E8</f>
-        <v>8.4670050761421312</v>
+        <v>7.9064039408867002</v>
       </c>
       <c r="H8">
-        <v>21.635189</v>
+        <v>22.494221</v>
       </c>
       <c r="I8">
-        <v>2.6482320000000001</v>
+        <v>2.9106960000000002</v>
       </c>
       <c r="J8">
-        <v>16.803374999999999</v>
+        <v>16.172581000000001</v>
       </c>
       <c r="K8">
-        <v>2.0567989999999998</v>
+        <v>2.0926909999999999</v>
       </c>
       <c r="L8">
         <f t="shared" si="5"/>
-        <v>8.1696728751812895</v>
+        <v>7.7281266082761393</v>
       </c>
       <c r="M8">
         <f t="shared" si="2"/>
-        <v>0.73965827338129098</v>
+        <v>0.76374454828660598</v>
       </c>
       <c r="N8">
         <f t="shared" si="3"/>
-        <v>4.4060406091370483</v>
+        <v>3.0882266009852244</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>3.5116572895255285</v>
+        <v>2.2548472598095861</v>
       </c>
       <c r="P8">
         <f t="shared" si="1"/>
-        <v>82.97878787878787</v>
+        <v>83.542307692307688</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -943,57 +943,57 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="C9">
         <f t="shared" si="4"/>
-        <v>39.6</v>
+        <v>40.800000000000004</v>
       </c>
       <c r="D9">
-        <v>16.91</v>
+        <v>16.489999999999998</v>
       </c>
       <c r="E9">
-        <v>1.96</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F9">
         <f>D9*E9</f>
-        <v>33.143599999999999</v>
+        <v>33.804499999999997</v>
       </c>
       <c r="G9">
         <f t="shared" ref="G9" si="10">D9/E9</f>
-        <v>8.6275510204081627</v>
+        <v>8.0439024390243894</v>
       </c>
       <c r="H9">
-        <v>21.63496</v>
+        <v>22.784503999999998</v>
       </c>
       <c r="I9">
-        <v>2.5913940000000002</v>
+        <v>2.841723</v>
       </c>
       <c r="J9">
-        <v>17.031825999999999</v>
+        <v>16.606221999999999</v>
       </c>
       <c r="K9">
-        <v>2.0400399999999999</v>
+        <v>2.0711569999999999</v>
       </c>
       <c r="L9">
         <f t="shared" ref="L9" si="11">J9/K9</f>
-        <v>8.3487706123409353</v>
+        <v>8.0178479951061163</v>
       </c>
       <c r="M9">
         <f t="shared" si="2"/>
-        <v>0.72043761088112745</v>
+        <v>0.70480291085506674</v>
       </c>
       <c r="N9">
         <f t="shared" si="3"/>
-        <v>4.0836734693877492</v>
+        <v>1.0320487804878093</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>3.2312808977632508</v>
+        <v>0.32390303233753648</v>
       </c>
       <c r="P9">
         <f t="shared" si="1"/>
-        <v>83.695959595959593</v>
+        <v>82.854166666666657</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1001,57 +1001,57 @@
         <v>60</v>
       </c>
       <c r="B10">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="C10">
         <f t="shared" si="4"/>
-        <v>40.200000000000003</v>
+        <v>40.800000000000004</v>
       </c>
       <c r="D10">
-        <v>17.16</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="E10">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <f>D10*E10</f>
-        <v>32.775599999999997</v>
+        <v>33.979999999999997</v>
       </c>
       <c r="G10">
         <f>D10/E10</f>
-        <v>8.9842931937172779</v>
+        <v>8.4949999999999992</v>
       </c>
       <c r="H10">
-        <v>21.636126999999998</v>
+        <v>22.493919000000002</v>
       </c>
       <c r="I10">
-        <v>2.528483</v>
+        <v>2.6759400000000002</v>
       </c>
       <c r="J10">
-        <v>17.267949999999999</v>
+        <v>17.095009000000001</v>
       </c>
       <c r="K10">
-        <v>2.0180009999999999</v>
+        <v>2.0336699999999999</v>
       </c>
       <c r="L10">
         <f t="shared" si="5"/>
-        <v>8.5569580986332507</v>
+        <v>8.4059896640064533</v>
       </c>
       <c r="M10">
         <f t="shared" si="2"/>
-        <v>0.62907925407924759</v>
+        <v>0.61806356680401753</v>
       </c>
       <c r="N10">
         <f t="shared" si="3"/>
-        <v>5.6545026178010476</v>
+        <v>1.6834999999999933</v>
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>4.7564687156788565</v>
+        <v>1.0477967744973031</v>
       </c>
       <c r="P10">
         <f t="shared" si="1"/>
-        <v>81.531343283582075</v>
+        <v>83.284313725490179</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1059,57 +1059,57 @@
         <v>60</v>
       </c>
       <c r="B11">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="C11">
         <f t="shared" si="4"/>
-        <v>39.6</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="D11">
-        <v>17.48</v>
+        <v>17.41</v>
       </c>
       <c r="E11">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="F11">
         <f>D11*E11</f>
-        <v>32.687600000000003</v>
+        <v>33.775399999999998</v>
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>9.3475935828877006</v>
+        <v>8.9742268041237114</v>
       </c>
       <c r="H11">
-        <v>21.636707000000001</v>
+        <v>22.494114</v>
       </c>
       <c r="I11">
-        <v>2.436547</v>
+        <v>2.549509</v>
       </c>
       <c r="J11">
-        <v>17.583126</v>
+        <v>17.511776000000001</v>
       </c>
       <c r="K11">
-        <v>1.9800660000000001</v>
+        <v>1.9848049999999999</v>
       </c>
       <c r="L11">
         <f t="shared" si="5"/>
-        <v>8.8800706643111891</v>
+        <v>8.8229201357312181</v>
       </c>
       <c r="M11">
         <f t="shared" si="2"/>
-        <v>0.58996567505720598</v>
+        <v>0.58458357265939676</v>
       </c>
       <c r="N11">
         <f t="shared" si="3"/>
-        <v>5.8858823529411763</v>
+        <v>2.3095360824742261</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>5.0015323669226346</v>
+        <v>1.6860134214901605</v>
       </c>
       <c r="P11">
         <f t="shared" si="1"/>
-        <v>82.544444444444451</v>
+        <v>84.018407960198999</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1117,57 +1117,57 @@
         <v>60</v>
       </c>
       <c r="B12">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="C12">
         <f t="shared" si="4"/>
-        <v>39.6</v>
+        <v>39</v>
       </c>
       <c r="D12">
-        <v>17.850000000000001</v>
+        <v>17.97</v>
       </c>
       <c r="E12">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="F12">
         <f>D12*E12</f>
-        <v>32.844000000000001</v>
+        <v>32.525700000000001</v>
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>9.7010869565217401</v>
+        <v>9.928176795580109</v>
       </c>
       <c r="H12">
-        <v>21.637428</v>
+        <v>22.494651999999999</v>
       </c>
       <c r="I12">
-        <v>2.3184450000000001</v>
+        <v>2.3565119999999999</v>
       </c>
       <c r="J12">
-        <v>17.934850999999998</v>
+        <v>18.038937000000001</v>
       </c>
       <c r="K12">
-        <v>1.9217150000000001</v>
+        <v>1.889737</v>
       </c>
       <c r="L12">
         <f t="shared" si="5"/>
-        <v>9.3327319607746198</v>
+        <v>9.5457394335825576</v>
       </c>
       <c r="M12">
         <f t="shared" si="2"/>
-        <v>0.47535574229690136</v>
+        <v>0.38362270450752256</v>
       </c>
       <c r="N12">
         <f t="shared" si="3"/>
-        <v>4.4410326086956511</v>
+        <v>4.4053591160220966</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>3.7970486956565908</v>
+        <v>3.85204020709832</v>
       </c>
       <c r="P12">
         <f t="shared" si="1"/>
-        <v>82.939393939393938</v>
+        <v>83.399230769230769</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1175,57 +1175,57 @@
         <v>60</v>
       </c>
       <c r="B13">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="C13">
         <f t="shared" si="4"/>
-        <v>37.799999999999997</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D13">
-        <v>18.25</v>
+        <v>18.36</v>
       </c>
       <c r="E13">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="F13">
         <f t="shared" ref="F13:F14" si="12">D13*E13</f>
-        <v>31.9375</v>
+        <v>31.212</v>
       </c>
       <c r="G13">
         <f>D13/E13</f>
-        <v>10.428571428571429</v>
+        <v>10.8</v>
       </c>
       <c r="H13">
-        <v>21.635871999999999</v>
+        <v>22.495331</v>
       </c>
       <c r="I13">
-        <v>2.1685469999999998</v>
+        <v>2.1689919999999998</v>
       </c>
       <c r="J13">
-        <v>18.304523</v>
+        <v>18.432518000000002</v>
       </c>
       <c r="K13">
-        <v>1.834649</v>
+        <v>1.7772570000000001</v>
       </c>
       <c r="L13">
         <f t="shared" si="5"/>
-        <v>9.9771253247896468</v>
+        <v>10.371329526343123</v>
       </c>
       <c r="M13">
         <f t="shared" si="2"/>
-        <v>0.29875616438355973</v>
+        <v>0.39497821350763784</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
-        <v>4.8370857142857124</v>
+        <v>4.5445294117647137</v>
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>4.3289352417431157</v>
+        <v>3.969171052378496</v>
       </c>
       <c r="P13">
         <f t="shared" si="1"/>
-        <v>84.490740740740748</v>
+        <v>83.903225806451616</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1233,57 +1233,57 @@
         <v>60</v>
       </c>
       <c r="B14">
-        <v>0.59</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="C14">
         <f t="shared" si="4"/>
-        <v>35.4</v>
+        <v>34.199999999999996</v>
       </c>
       <c r="D14">
-        <v>18.739999999999998</v>
+        <v>18.78</v>
       </c>
       <c r="E14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="F14">
         <f t="shared" si="12"/>
-        <v>29.421799999999998</v>
+        <v>28.733400000000003</v>
       </c>
       <c r="G14">
         <f>D14/E14</f>
-        <v>11.936305732484074</v>
+        <v>12.274509803921569</v>
       </c>
       <c r="H14">
-        <v>21.640063999999999</v>
+        <v>22.497145</v>
       </c>
       <c r="I14">
-        <v>1.9334210000000001</v>
+        <v>1.9506749999999999</v>
       </c>
       <c r="J14">
-        <v>18.780472</v>
+        <v>18.831503000000001</v>
       </c>
       <c r="K14">
-        <v>1.677932</v>
+        <v>1.632836</v>
       </c>
       <c r="L14">
         <f t="shared" si="5"/>
-        <v>11.192629975469805</v>
+        <v>11.533003314478615</v>
       </c>
       <c r="M14">
         <f t="shared" si="2"/>
-        <v>0.21596584845251426</v>
+        <v>0.2742438764643253</v>
       </c>
       <c r="N14">
         <f t="shared" si="3"/>
-        <v>6.8746496815286564</v>
+        <v>6.721307189542479</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>6.2303678682625581</v>
+        <v>6.0410273101582579</v>
       </c>
       <c r="P14">
         <f t="shared" si="1"/>
-        <v>83.112429378531075</v>
+        <v>84.015789473684237</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1298,50 +1298,50 @@
         <v>31.200000000000003</v>
       </c>
       <c r="D15">
-        <v>19.13</v>
+        <v>19.12</v>
       </c>
       <c r="E15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="F15">
         <f t="shared" ref="F15" si="13">D15*E15</f>
-        <v>25.6342</v>
+        <v>25.812000000000005</v>
       </c>
       <c r="G15">
         <f>D15/E15</f>
-        <v>14.276119402985072</v>
+        <v>14.162962962962963</v>
       </c>
       <c r="H15">
-        <v>21.643158</v>
+        <v>22.500510999999999</v>
       </c>
       <c r="I15">
-        <v>1.6755800000000001</v>
+        <v>1.7198439999999999</v>
       </c>
       <c r="J15">
-        <v>19.152412000000002</v>
+        <v>19.143657999999999</v>
       </c>
       <c r="K15">
-        <v>1.48275</v>
+        <v>1.46326</v>
       </c>
       <c r="L15">
         <f t="shared" si="5"/>
-        <v>12.91681807452369</v>
+        <v>13.08288205787078</v>
       </c>
       <c r="M15">
         <f t="shared" si="2"/>
-        <v>0.11715629900681006</v>
+        <v>0.12373430962341796</v>
       </c>
       <c r="N15">
         <f t="shared" si="3"/>
-        <v>10.65298507462686</v>
+        <v>8.3896296296296224</v>
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>9.5215043394576764</v>
+        <v>7.6260942566655192</v>
       </c>
       <c r="P15">
         <f t="shared" si="1"/>
-        <v>82.160897435897425</v>
+        <v>82.730769230769241</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1349,57 +1349,57 @@
         <v>60</v>
       </c>
       <c r="B16">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="C16">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="D16">
-        <v>19.5</v>
+        <v>19.48</v>
       </c>
       <c r="E16">
-        <v>1.1200000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F16">
         <f>D16*E16</f>
-        <v>21.840000000000003</v>
+        <v>22.2072</v>
       </c>
       <c r="G16">
         <f t="shared" ref="G16:G19" si="14">D16/E16</f>
-        <v>17.410714285714285</v>
+        <v>17.087719298245617</v>
       </c>
       <c r="H16">
-        <v>21.647424999999998</v>
+        <v>22.504716999999999</v>
       </c>
       <c r="I16">
-        <v>1.443203</v>
+        <v>1.4841310000000001</v>
       </c>
       <c r="J16">
-        <v>19.492190999999998</v>
+        <v>19.473244000000001</v>
       </c>
       <c r="K16">
-        <v>1.299517</v>
+        <v>1.284213</v>
       </c>
       <c r="L16">
         <f t="shared" ref="L16:L19" si="15">J16/K16</f>
-        <v>14.999565992595709</v>
+        <v>15.163562430842859</v>
       </c>
       <c r="M16">
         <f t="shared" si="2"/>
-        <v>4.0046153846162724E-2</v>
+        <v>3.4681724845992391E-2</v>
       </c>
       <c r="N16">
         <f t="shared" si="3"/>
-        <v>16.028303571428562</v>
+        <v>12.65026315789475</v>
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>13.848646606629767</v>
+        <v>11.260466267141393</v>
       </c>
       <c r="P16">
         <f t="shared" si="1"/>
-        <v>80.8888888888889</v>
+        <v>80.460869565217379</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1407,57 +1407,57 @@
         <v>60</v>
       </c>
       <c r="B17">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C19" si="16">A15*B17</f>
-        <v>18</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D17">
-        <v>19.899999999999999</v>
+        <v>19.86</v>
       </c>
       <c r="E17">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="F17">
         <f t="shared" ref="F17:F19" si="17">D17*E17</f>
-        <v>12.934999999999999</v>
+        <v>13.504800000000001</v>
       </c>
       <c r="G17">
         <f t="shared" si="14"/>
-        <v>30.615384615384613</v>
+        <v>29.205882352941174</v>
       </c>
       <c r="H17">
-        <v>21.917014999999999</v>
+        <v>22.512615</v>
       </c>
       <c r="I17">
-        <v>0.96918599999999999</v>
+        <v>0.99190299999999998</v>
       </c>
       <c r="J17">
-        <v>19.843899</v>
+        <v>19.819203999999999</v>
       </c>
       <c r="K17">
-        <v>0.87751199999999996</v>
+        <v>0.87323099999999998</v>
       </c>
       <c r="L17">
         <f t="shared" si="15"/>
-        <v>22.613820665700299</v>
+        <v>22.696404502359627</v>
       </c>
       <c r="M17">
         <f t="shared" si="2"/>
-        <v>0.28191457286431248</v>
+        <v>0.20541792547834983</v>
       </c>
       <c r="N17">
         <f t="shared" si="3"/>
-        <v>35.001846153846145</v>
+        <v>28.416323529411752</v>
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>26.13576164469751</v>
+        <v>22.288242388698148</v>
       </c>
       <c r="P17">
         <f t="shared" si="1"/>
-        <v>71.861111111111114</v>
+        <v>72.606451612903228</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1472,50 +1472,50 @@
         <v>9.6</v>
       </c>
       <c r="D18">
-        <v>20.32</v>
+        <v>20.28</v>
       </c>
       <c r="E18">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="F18">
         <f t="shared" si="17"/>
-        <v>3.4544000000000001</v>
+        <v>3.6503999999999999</v>
       </c>
       <c r="G18">
         <f t="shared" si="14"/>
-        <v>119.52941176470587</v>
+        <v>112.66666666666667</v>
       </c>
       <c r="H18">
-        <v>21.658646000000001</v>
+        <v>22.518124</v>
       </c>
       <c r="I18">
-        <v>0.47305700000000001</v>
+        <v>0.45316400000000001</v>
       </c>
       <c r="J18">
-        <v>20.207394000000001</v>
+        <v>20.202764999999999</v>
       </c>
       <c r="K18">
-        <v>0.441359</v>
+        <v>0.40656900000000001</v>
       </c>
       <c r="L18">
         <f t="shared" si="15"/>
-        <v>45.784483832888874</v>
+        <v>49.690864281339692</v>
       </c>
       <c r="M18">
         <f t="shared" si="2"/>
-        <v>0.55416338582676938</v>
+        <v>0.38084319526628063</v>
       </c>
       <c r="N18">
         <f t="shared" si="3"/>
-        <v>159.62294117647059</v>
+        <v>125.8716666666667</v>
       </c>
       <c r="O18">
         <f t="shared" si="0"/>
-        <v>61.696051911461069</v>
+        <v>55.89568259052691</v>
       </c>
       <c r="P18">
         <f t="shared" si="1"/>
-        <v>35.983333333333334</v>
+        <v>38.024999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1530,50 +1530,50 @@
         <v>7.1999999999999993</v>
       </c>
       <c r="D19">
-        <v>20.440000000000001</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E19">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F19">
         <f t="shared" si="17"/>
-        <v>0.8176000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="G19">
         <f t="shared" si="14"/>
-        <v>511</v>
+        <v>407.99999999999994</v>
       </c>
       <c r="H19">
-        <v>21.662161000000001</v>
+        <v>22.518229999999999</v>
       </c>
       <c r="I19">
-        <v>0.32171100000000002</v>
+        <v>0.31775900000000001</v>
       </c>
       <c r="J19">
-        <v>20.323677</v>
+        <v>20.301469999999998</v>
       </c>
       <c r="K19">
-        <v>0.30183300000000002</v>
+        <v>0.28647800000000001</v>
       </c>
       <c r="L19">
         <f t="shared" si="15"/>
-        <v>67.334178171372912</v>
+        <v>70.865720927959558</v>
       </c>
       <c r="M19">
         <f t="shared" si="2"/>
-        <v>0.56909491193738393</v>
+        <v>0.48299019607843258</v>
       </c>
       <c r="N19">
         <f t="shared" si="3"/>
-        <v>654.5825000000001</v>
+        <v>472.95600000000002</v>
       </c>
       <c r="O19">
         <f t="shared" si="0"/>
-        <v>86.823057109320374</v>
+        <v>82.63095075295108</v>
       </c>
       <c r="P19">
         <f t="shared" si="1"/>
-        <v>11.355555555555558</v>
+        <v>14.16666666666667</v>
       </c>
     </row>
   </sheetData>
